--- a/GUI/Example_Scaling_FusionFS980.xlsx
+++ b/GUI/Example_Scaling_FusionFS980.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ReiterTo\Documents\Arduino\Simulink_InverterV3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ReiterTo\Documents\Arduino\Arduino_Inverter_GIT\GUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B83173B-AEEC-4BE3-9483-FF76A9A971AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CD7D12-D87B-4404-B739-77B73D3CA4DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="11940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Vdc_RawOffset [RAW]</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Vdc_Vgain [V/V]</t>
   </si>
   <si>
-    <t>Temp_RawOffset [RAW]</t>
-  </si>
-  <si>
     <t>Temp_Raw2Volt [V/RAW]</t>
   </si>
   <si>
@@ -44,6 +41,12 @@
   </si>
   <si>
     <t>Current [A/RAW]</t>
+  </si>
+  <si>
+    <t>Temp_RawOffset_LS [RAW]</t>
+  </si>
+  <si>
+    <t>Temp_RawOffset_HS [RAW]</t>
   </si>
 </sst>
 </file>
@@ -392,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
@@ -425,7 +428,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>565</v>
@@ -433,33 +436,41 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>3.4860000000000002E-4</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>2.2799999999999998</v>
+        <v>3.4860000000000002E-4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>-5.5</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
         <v>0.1</v>
       </c>
     </row>
